--- a/diseases/d010/2015-2019.xlsx
+++ b/diseases/d010/2015-2019.xlsx
@@ -7976,7 +7976,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20148,7 +20148,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21484,7 +21484,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25640,7 +25640,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26976,7 +26976,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28312,7 +28312,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29648,7 +29648,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30984,7 +30984,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32320,7 +32320,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -33656,7 +33656,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34992,7 +34992,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -36328,7 +36328,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37664,7 +37664,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -39000,7 +39000,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40336,7 +40336,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41672,7 +41672,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43008,7 +43008,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -44344,7 +44344,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -45680,7 +45680,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -47016,7 +47016,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48352,7 +48352,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49688,7 +49688,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -51024,7 +51024,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -52360,7 +52360,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53696,7 +53696,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -55032,7 +55032,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -56368,7 +56368,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -57704,7 +57704,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -59040,7 +59040,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -60376,7 +60376,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -61712,7 +61712,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -63048,7 +63048,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -64384,7 +64384,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -65720,7 +65720,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -67056,7 +67056,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -68392,7 +68392,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -69728,7 +69728,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -71064,7 +71064,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">

--- a/diseases/d010/2015-2019.xlsx
+++ b/diseases/d010/2015-2019.xlsx
@@ -7976,7 +7976,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18812,7 +18812,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20148,7 +20148,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21484,7 +21484,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25640,7 +25640,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26976,7 +26976,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28312,7 +28312,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29648,7 +29648,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30984,7 +30984,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32320,7 +32320,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -33656,7 +33656,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34992,7 +34992,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -36328,7 +36328,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37664,7 +37664,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -39000,7 +39000,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40336,7 +40336,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41672,7 +41672,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43008,7 +43008,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -44344,7 +44344,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -45680,7 +45680,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -47016,7 +47016,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48352,7 +48352,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49688,7 +49688,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -51024,7 +51024,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -52360,7 +52360,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53696,7 +53696,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -55032,7 +55032,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -56368,7 +56368,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -57704,7 +57704,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -59040,7 +59040,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -60376,7 +60376,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -61712,7 +61712,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -63048,7 +63048,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -64384,7 +64384,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -65720,7 +65720,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -67056,7 +67056,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -68392,7 +68392,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -69728,7 +69728,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -71064,7 +71064,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">

--- a/diseases/d010/2015-2019.xlsx
+++ b/diseases/d010/2015-2019.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2001,9 +1995,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2693,9 +2684,6 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.01824911594438947</v>
       </c>
@@ -3237,9 +3225,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3781,9 +3766,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -4325,9 +4307,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4869,9 +4848,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5413,9 +5389,6 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.01824911594438947</v>
       </c>
@@ -5957,9 +5930,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6649,9 +6619,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7193,9 +7160,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -8133,9 +8097,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -8529,9 +8490,6 @@
       <c r="O45" t="n">
         <v>10</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.1007731314645964</v>
       </c>
@@ -9469,9 +9427,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.01819680904395967</v>
       </c>
@@ -9865,9 +9820,6 @@
       <c r="O52" t="n">
         <v>6</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.06046387887875783</v>
       </c>
@@ -10953,9 +10905,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -11349,9 +11298,6 @@
       <c r="O60" t="n">
         <v>8</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.0806185051716771</v>
       </c>
@@ -12289,9 +12235,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -12685,9 +12628,6 @@
       <c r="O67" t="n">
         <v>6</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.06046387887875783</v>
       </c>
@@ -13625,9 +13565,6 @@
       <c r="O72" t="n">
         <v>4</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.07278723617583868</v>
       </c>
@@ -14021,9 +13958,6 @@
       <c r="O74" t="n">
         <v>4</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.04030925258583855</v>
       </c>
@@ -14961,9 +14895,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -15357,9 +15288,6 @@
       <c r="O81" t="n">
         <v>10</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.1007731314645964</v>
       </c>
@@ -16297,9 +16225,6 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.01819680904395967</v>
       </c>
@@ -16693,9 +16618,6 @@
       <c r="O88" t="n">
         <v>3</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.03023193943937891</v>
       </c>
@@ -17633,9 +17555,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -18029,9 +17948,6 @@
       <c r="O95" t="n">
         <v>6</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.06046387887875783</v>
       </c>
@@ -18969,9 +18885,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -19365,9 +19278,6 @@
       <c r="O102" t="n">
         <v>6</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.06046387887875783</v>
       </c>
@@ -20305,9 +20215,6 @@
       <c r="O107" t="n">
         <v>3</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.054590427131879</v>
       </c>
@@ -20701,9 +20608,6 @@
       <c r="O109" t="n">
         <v>4</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.04030925258583855</v>
       </c>
@@ -21641,9 +21545,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -22037,9 +21938,6 @@
       <c r="O116" t="n">
         <v>7</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.07054119202521747</v>
       </c>
@@ -22977,9 +22875,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -23373,9 +23268,6 @@
       <c r="O123" t="n">
         <v>7</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.07054119202521747</v>
       </c>
@@ -24461,9 +24353,6 @@
       <c r="O129" t="n">
         <v>1</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.01815410511517327</v>
       </c>
@@ -24857,9 +24746,6 @@
       <c r="O131" t="n">
         <v>4</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.03976988547714641</v>
       </c>
@@ -25797,9 +25683,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -26193,9 +26076,6 @@
       <c r="O138" t="n">
         <v>2</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.01988494273857321</v>
       </c>
@@ -27133,9 +27013,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -27529,9 +27406,6 @@
       <c r="O145" t="n">
         <v>5</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.04971235684643301</v>
       </c>
@@ -28469,9 +28343,6 @@
       <c r="O150" t="n">
         <v>1</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.01815410511517327</v>
       </c>
@@ -28865,9 +28736,6 @@
       <c r="O152" t="n">
         <v>6</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.05965482821571962</v>
       </c>
@@ -29805,9 +29673,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -30201,9 +30066,6 @@
       <c r="O159" t="n">
         <v>3</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.02982741410785981</v>
       </c>
@@ -31141,9 +31003,6 @@
       <c r="O164" t="n">
         <v>1</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.01815410511517327</v>
       </c>
@@ -31537,9 +31396,6 @@
       <c r="O166" t="n">
         <v>5</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.04971235684643301</v>
       </c>
@@ -32477,9 +32333,6 @@
       <c r="O171" t="n">
         <v>1</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.01815410511517327</v>
       </c>
@@ -32873,9 +32726,6 @@
       <c r="O173" t="n">
         <v>4</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.03976988547714641</v>
       </c>
@@ -33813,9 +33663,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -34209,9 +34056,6 @@
       <c r="O180" t="n">
         <v>6</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.05965482821571962</v>
       </c>
@@ -35149,9 +34993,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -35545,9 +35386,6 @@
       <c r="O187" t="n">
         <v>4</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.03976988547714641</v>
       </c>
@@ -36485,9 +36323,6 @@
       <c r="O192" t="n">
         <v>1</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.01815410511517327</v>
       </c>
@@ -36881,9 +36716,6 @@
       <c r="O194" t="n">
         <v>9</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.08948224232357942</v>
       </c>
@@ -37821,9 +37653,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -38217,9 +38046,6 @@
       <c r="O201" t="n">
         <v>3</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.02982741410785981</v>
       </c>
@@ -39157,9 +38983,6 @@
       <c r="O206" t="n">
         <v>1</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.01815410511517327</v>
       </c>
@@ -39553,9 +39376,6 @@
       <c r="O208" t="n">
         <v>3</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.02982741410785981</v>
       </c>
@@ -40493,9 +40313,6 @@
       <c r="O213" t="n">
         <v>2</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.03625989022499534</v>
       </c>
@@ -40889,9 +40706,6 @@
       <c r="O215" t="n">
         <v>9</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.08844857224103474</v>
       </c>
@@ -41829,9 +41643,6 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -42225,9 +42036,6 @@
       <c r="O222" t="n">
         <v>8</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.07862095310314199</v>
       </c>
@@ -43165,9 +42973,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
@@ -43561,9 +43366,6 @@
       <c r="O229" t="n">
         <v>6</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0.0589657148273565</v>
       </c>
@@ -44501,9 +44303,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -44897,9 +44696,6 @@
       <c r="O236" t="n">
         <v>7</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.06879333396524925</v>
       </c>
@@ -45837,9 +45633,6 @@
       <c r="O241" t="n">
         <v>1</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0.01812994511249767</v>
       </c>
@@ -46233,9 +46026,6 @@
       <c r="O243" t="n">
         <v>3</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.02948285741367825</v>
       </c>
@@ -47173,9 +46963,6 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -47569,9 +47356,6 @@
       <c r="O250" t="n">
         <v>3</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.02948285741367825</v>
       </c>
@@ -48509,9 +48293,6 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -48905,9 +48686,6 @@
       <c r="O257" t="n">
         <v>4</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0.03931047655157099</v>
       </c>
@@ -49845,9 +49623,6 @@
       <c r="O262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0</v>
       </c>
@@ -50241,9 +50016,6 @@
       <c r="O264" t="n">
         <v>4</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0.03931047655157099</v>
       </c>
@@ -51181,9 +50953,6 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -51577,9 +51346,6 @@
       <c r="O271" t="n">
         <v>7</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0.06879333396524925</v>
       </c>
@@ -52517,9 +52283,6 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
@@ -52913,9 +52676,6 @@
       <c r="O278" t="n">
         <v>12</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.117931429654713</v>
       </c>
@@ -53853,9 +53613,6 @@
       <c r="O283" t="n">
         <v>1</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0.01812994511249767</v>
       </c>
@@ -54249,9 +54006,6 @@
       <c r="O285" t="n">
         <v>8</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.07862095310314199</v>
       </c>
@@ -55189,9 +54943,6 @@
       <c r="O290" t="n">
         <v>0</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0</v>
       </c>
@@ -55585,9 +55336,6 @@
       <c r="O292" t="n">
         <v>1</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.009827619137892749</v>
       </c>
@@ -56525,9 +56273,6 @@
       <c r="O297" t="n">
         <v>0</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0</v>
       </c>
@@ -56921,9 +56666,6 @@
       <c r="O299" t="n">
         <v>11</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0.1070129996473435</v>
       </c>
@@ -57861,9 +57603,6 @@
       <c r="O304" t="n">
         <v>0</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0</v>
       </c>
@@ -58257,9 +57996,6 @@
       <c r="O306" t="n">
         <v>3</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0.0291853635401846</v>
       </c>
@@ -59197,9 +58933,6 @@
       <c r="O311" t="n">
         <v>0</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0</v>
       </c>
@@ -59593,9 +59326,6 @@
       <c r="O313" t="n">
         <v>6</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0.0583707270803692</v>
       </c>
@@ -60533,9 +60263,6 @@
       <c r="O318" t="n">
         <v>0</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0</v>
       </c>
@@ -60929,9 +60656,6 @@
       <c r="O320" t="n">
         <v>5</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0.04864227256697433</v>
       </c>
@@ -61869,9 +61593,6 @@
       <c r="O325" t="n">
         <v>0</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0</v>
       </c>
@@ -62265,9 +61986,6 @@
       <c r="O327" t="n">
         <v>3</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0.0291853635401846</v>
       </c>
@@ -63205,9 +62923,6 @@
       <c r="O332" t="n">
         <v>0</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>0</v>
       </c>
@@ -63601,9 +63316,6 @@
       <c r="O334" t="n">
         <v>3</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0.0291853635401846</v>
       </c>
@@ -64541,9 +64253,6 @@
       <c r="O339" t="n">
         <v>0</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0</v>
       </c>
@@ -64937,9 +64646,6 @@
       <c r="O341" t="n">
         <v>8</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0.07782763610715893</v>
       </c>
@@ -65877,9 +65583,6 @@
       <c r="O346" t="n">
         <v>0</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0</v>
       </c>
@@ -66273,9 +65976,6 @@
       <c r="O348" t="n">
         <v>2</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0.01945690902678973</v>
       </c>
@@ -67213,9 +66913,6 @@
       <c r="O353" t="n">
         <v>2</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0.03622034210475322</v>
       </c>
@@ -67609,9 +67306,6 @@
       <c r="O355" t="n">
         <v>10</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0.09728454513394866</v>
       </c>
@@ -68549,9 +68243,6 @@
       <c r="O360" t="n">
         <v>0</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0</v>
       </c>
@@ -68945,9 +68636,6 @@
       <c r="O362" t="n">
         <v>8</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0.07782763610715893</v>
       </c>
@@ -69885,9 +69573,6 @@
       <c r="O367" t="n">
         <v>0</v>
       </c>
-      <c r="Q367" t="n">
-        <v>0</v>
-      </c>
       <c r="R367" t="n">
         <v>0</v>
       </c>
@@ -70281,9 +69966,6 @@
       <c r="O369" t="n">
         <v>4</v>
       </c>
-      <c r="Q369" t="n">
-        <v>0</v>
-      </c>
       <c r="R369" t="n">
         <v>0.03891381805357946</v>
       </c>
@@ -71221,9 +70903,6 @@
       <c r="O374" t="n">
         <v>0</v>
       </c>
-      <c r="Q374" t="n">
-        <v>0</v>
-      </c>
       <c r="R374" t="n">
         <v>0</v>
       </c>
@@ -71616,9 +71295,6 @@
       </c>
       <c r="O376" t="n">
         <v>7</v>
-      </c>
-      <c r="Q376" t="n">
-        <v>0</v>
       </c>
       <c r="R376" t="n">
         <v>0.06809918159376406</v>

--- a/diseases/d010/2015-2019.xlsx
+++ b/diseases/d010/2015-2019.xlsx
@@ -7940,7 +7940,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17398,7 +17398,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25526,7 +25526,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26856,7 +26856,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28186,7 +28186,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30846,7 +30846,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32176,7 +32176,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -33506,7 +33506,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34836,7 +34836,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37496,7 +37496,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38826,7 +38826,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40156,7 +40156,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41486,7 +41486,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -42816,7 +42816,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -44146,7 +44146,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -45476,7 +45476,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46806,7 +46806,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48136,7 +48136,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49466,7 +49466,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -50796,7 +50796,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -52126,7 +52126,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53456,7 +53456,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -54786,7 +54786,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -56116,7 +56116,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -57446,7 +57446,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -58776,7 +58776,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -60106,7 +60106,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -61436,7 +61436,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -62766,7 +62766,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -64096,7 +64096,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -65426,7 +65426,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -66756,7 +66756,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -68086,7 +68086,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -69416,7 +69416,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -70746,7 +70746,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">

--- a/diseases/d010/2015-2019.xlsx
+++ b/diseases/d010/2015-2019.xlsx
@@ -7940,7 +7940,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17398,7 +17398,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25526,7 +25526,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26856,7 +26856,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28186,7 +28186,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30846,7 +30846,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32176,7 +32176,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -33506,7 +33506,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34836,7 +34836,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37496,7 +37496,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38826,7 +38826,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40156,7 +40156,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41486,7 +41486,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -42816,7 +42816,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -44146,7 +44146,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -45476,7 +45476,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46806,7 +46806,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48136,7 +48136,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49466,7 +49466,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -50796,7 +50796,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -52126,7 +52126,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53456,7 +53456,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -54786,7 +54786,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -56116,7 +56116,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -57446,7 +57446,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -58776,7 +58776,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -60106,7 +60106,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -61436,7 +61436,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -62766,7 +62766,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -64096,7 +64096,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -65426,7 +65426,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -66756,7 +66756,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -68086,7 +68086,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -69416,7 +69416,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -70746,7 +70746,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">

--- a/diseases/d010/2015-2019.xlsx
+++ b/diseases/d010/2015-2019.xlsx
@@ -7940,7 +7940,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17398,7 +17398,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25526,7 +25526,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26856,7 +26856,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28186,7 +28186,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30846,7 +30846,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32176,7 +32176,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -33506,7 +33506,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34836,7 +34836,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37496,7 +37496,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38826,7 +38826,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40156,7 +40156,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41486,7 +41486,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -42816,7 +42816,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -44146,7 +44146,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -45476,7 +45476,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46806,7 +46806,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48136,7 +48136,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49466,7 +49466,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -50796,7 +50796,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -52126,7 +52126,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53456,7 +53456,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -54786,7 +54786,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -56116,7 +56116,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -57446,7 +57446,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -58776,7 +58776,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -60106,7 +60106,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -61436,7 +61436,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -62766,7 +62766,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -64096,7 +64096,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -65426,7 +65426,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -66756,7 +66756,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -68086,7 +68086,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -69416,7 +69416,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -70746,7 +70746,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">

--- a/diseases/d010/2015-2019.xlsx
+++ b/diseases/d010/2015-2019.xlsx
@@ -7940,7 +7940,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17398,7 +17398,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25526,7 +25526,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26856,7 +26856,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28186,7 +28186,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30846,7 +30846,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32176,7 +32176,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -33506,7 +33506,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34836,7 +34836,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37496,7 +37496,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38826,7 +38826,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40156,7 +40156,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41486,7 +41486,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -42816,7 +42816,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -44146,7 +44146,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -45476,7 +45476,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46806,7 +46806,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48136,7 +48136,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49466,7 +49466,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -50796,7 +50796,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -52126,7 +52126,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -53456,7 +53456,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -54786,7 +54786,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -56116,7 +56116,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -57446,7 +57446,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -58776,7 +58776,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -60106,7 +60106,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -61436,7 +61436,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -62766,7 +62766,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -64096,7 +64096,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -65426,7 +65426,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -66756,7 +66756,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -68086,7 +68086,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -69416,7 +69416,7 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
@@ -70746,7 +70746,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
